--- a/web/public/Mau_Don_Gia.xlsx
+++ b/web/public/Mau_Don_Gia.xlsx
@@ -37,7 +37,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFBEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -81,14 +86,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -458,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -622,30 +629,56 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Đào tạo an toàn lao động</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Không tính sản lượng</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>công</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Đào tạo</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Xử lý phát sinh tại hiện trường</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Không tính sản lượng</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>công</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>KHÁC MẪU</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Phát sinh</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -658,93 +691,107 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN NHẬP LIỆU</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>1. Cột có dấu * là BẮT BUỘC. Không được để trống.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2. Khóa duy nhất của mỗi dòng = Hạng mục thi công (Cấp 1) + Nội dung công việc (Cấp 2). Trùng khóa -&gt; hệ thống báo lỗi DUPLICATE_PRICE_KEY và KHÔNG ghi gì cả.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>3. Cột 'Đơn giá NC dùng tính toán' là con số hệ thống dùng để tính sản lượng, hòa vốn và lãi/lỗ (đã bao gồm hệ số +30%). Nhập đúng số, không nhập công thức, không nhập chữ 'đ' hay dấu chấm phân cách.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>4. Hệ thống tự suy ra 'Đơn giá đã duyệt' = Đơn giá dùng tính toán / 1.3 (chỉ để tham khảo và truy vết).</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>5. Không dùng ký tự ‡ trong bất kỳ ô nào — đây là ký tự hệ thống dùng làm khóa tra cứu.</t>
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>5. VIỆC ĐẶC BIỆT (2 dòng tô vàng): hệ thống nhận biết việc không tính sản lượng qua HẠNG MỤC CẤP 1 đặt đúng tên 'Đào tạo' hoặc 'Phát sinh'. Nếu bạn để 'Đào tạo' ở cột Nội dung Cấp 2 mà hạng mục Cấp 1 lại là tên khác thì hệ thống KHÔNG coi đó là việc đặc biệt.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>6. Hạng mục Cấp 1 mới trong file sẽ được tạo tự động.</t>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>6. Giữ đủ hai hạng mục 'Đào tạo' và 'Phát sinh' trong file, nếu không người dùng sẽ không giao được loại việc này (báo lỗi INVALID_CATEGORY).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>7. Dòng cũ không còn trong file: nếu đang được một công việc chưa xóa sử dụng thì GIỮ NGUYÊN để không phá KPI; còn lại chuyển sang trạng thái ngừng dùng. Không dòng nào bị xóa cứng.</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>7. Không dùng ký tự ‡ trong bất kỳ ô nào — đây là ký tự hệ thống dùng làm khóa tra cứu.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>8. Toàn bộ file được kiểm tra trước khi ghi. Chỉ cần MỘT dòng sai là không có thay đổi nào được lưu — dữ liệu cũ giữ nguyên.</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>8. Hạng mục Cấp 1 mới trong file sẽ được tạo tự động.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>9. Trước mỗi lần nhập, hệ thống tự chụp ảnh (snapshot) toàn bộ đơn giá cũ để phục hồi khi cần.</t>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>9. Dòng cũ không còn trong file: nếu đang được một công việc chưa xóa sử dụng thì GIỮ NGUYÊN để không phá KPI; còn lại chuyển sang trạng thái ngừng dùng. Không dòng nào bị xóa cứng. Nạp lại file có dòng đó sẽ kích hoạt lại.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>10. Bấm nhiều lần cùng một file chỉ ghi một lần (chống double-click bằng request_key + SHA-256).</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10. Toàn bộ file được kiểm tra trước khi ghi. Chỉ cần MỘT dòng sai là không có thay đổi nào được lưu — dữ liệu cũ giữ nguyên.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>11. Chỉ tài khoản ADMIN được nhập file này.</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11. Trước mỗi lần nhập, hệ thống tự chụp ảnh (snapshot) toàn bộ đơn giá cũ để phục hồi khi cần.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>12. Bấm nhiều lần cùng một file chỉ ghi một lần (chống double-click bằng request_key + SHA-256).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>13. Chỉ tài khoản ADMIN được nhập file này.</t>
         </is>
       </c>
     </row>

--- a/web/public/Mau_Don_Gia.xlsx
+++ b/web/public/Mau_Don_Gia.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -711,85 +711,92 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>2. Khóa duy nhất của mỗi dòng = Hạng mục thi công (Cấp 1) + Nội dung công việc (Cấp 2). Trùng khóa -&gt; hệ thống báo lỗi DUPLICATE_PRICE_KEY và KHÔNG ghi gì cả.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>2. Khóa duy nhất của mỗi dòng = Hạng mục thi công (Cấp 1) + Nội dung công việc (Cấp 2), so sánh ĐÚNG NGUYÊN VĂN. Hai tên chỉ khác nhau ở dấu gạch nối, khoảng trắng hay ký hiệu (ví dụ 'D90 - PN8' và 'D90 – PN6') là HAI DÒNG KHÁC NHAU, không phải trùng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>3. Cột 'Đơn giá NC dùng tính toán' là con số hệ thống dùng để tính sản lượng, hòa vốn và lãi/lỗ (đã bao gồm hệ số +30%). Nhập đúng số, không nhập công thức, không nhập chữ 'đ' hay dấu chấm phân cách.</t>
+          <t>2b. Chỉ khi Hạng mục Cấp 1 + Nội dung Cấp 2 + Đơn giá đều giống hệt thì mới là dòng lặp — hệ thống tự bỏ qua, không báo lỗi. Nếu cùng tên mà KHÁC đơn giá thì dừng và báo rõ tên nào, vì mỗi công việc chỉ lưu được một đơn giá; để hai giá thì lúc tính hòa vốn hệ thống không biết lấy giá nào. Muốn hai mức giá thì đặt hai tên công việc khác nhau.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>4. Hệ thống tự suy ra 'Đơn giá đã duyệt' = Đơn giá dùng tính toán / 1.3 (chỉ để tham khảo và truy vết).</t>
+          <t>3. Cột 'Đơn giá NC dùng tính toán' là con số hệ thống dùng để tính sản lượng, hòa vốn và lãi/lỗ (đã bao gồm hệ số +30%). Nhập đúng số, không nhập công thức, không nhập chữ 'đ' hay dấu chấm phân cách.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>5. VIỆC ĐẶC BIỆT (2 dòng tô vàng): hệ thống nhận biết việc không tính sản lượng qua HẠNG MỤC CẤP 1 đặt đúng tên 'Đào tạo' hoặc 'Phát sinh'. Nếu bạn để 'Đào tạo' ở cột Nội dung Cấp 2 mà hạng mục Cấp 1 lại là tên khác thì hệ thống KHÔNG coi đó là việc đặc biệt.</t>
+          <t>4. Hệ thống tự suy ra 'Đơn giá đã duyệt' = Đơn giá dùng tính toán / 1.3 (chỉ để tham khảo và truy vết).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>6. Giữ đủ hai hạng mục 'Đào tạo' và 'Phát sinh' trong file, nếu không người dùng sẽ không giao được loại việc này (báo lỗi INVALID_CATEGORY).</t>
+          <t>5. VIỆC ĐẶC BIỆT (2 dòng tô vàng): hệ thống nhận biết việc không tính sản lượng qua HẠNG MỤC CẤP 1 đặt đúng tên 'Đào tạo' hoặc 'Phát sinh'. Nếu bạn để 'Đào tạo' ở cột Nội dung Cấp 2 mà hạng mục Cấp 1 lại là tên khác thì hệ thống KHÔNG coi đó là việc đặc biệt.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>7. Không dùng ký tự ‡ trong bất kỳ ô nào — đây là ký tự hệ thống dùng làm khóa tra cứu.</t>
+          <t>6. Giữ đủ hai hạng mục 'Đào tạo' và 'Phát sinh' trong file, nếu không người dùng sẽ không giao được loại việc này (báo lỗi INVALID_CATEGORY).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>8. Hạng mục Cấp 1 mới trong file sẽ được tạo tự động.</t>
+          <t>7. Không dùng ký tự ‡ trong bất kỳ ô nào — đây là ký tự hệ thống dùng làm khóa tra cứu.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>9. Dòng cũ không còn trong file: nếu đang được một công việc chưa xóa sử dụng thì GIỮ NGUYÊN để không phá KPI; còn lại chuyển sang trạng thái ngừng dùng. Không dòng nào bị xóa cứng. Nạp lại file có dòng đó sẽ kích hoạt lại.</t>
+          <t>8. Hạng mục Cấp 1 mới trong file sẽ được tạo tự động.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>10. Toàn bộ file được kiểm tra trước khi ghi. Chỉ cần MỘT dòng sai là không có thay đổi nào được lưu — dữ liệu cũ giữ nguyên.</t>
+          <t>9. Dòng cũ không còn trong file: nếu đang được một công việc chưa xóa sử dụng thì GIỮ NGUYÊN để không phá KPI; còn lại chuyển sang trạng thái ngừng dùng. Không dòng nào bị xóa cứng. Nạp lại file có dòng đó sẽ kích hoạt lại.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>11. Trước mỗi lần nhập, hệ thống tự chụp ảnh (snapshot) toàn bộ đơn giá cũ để phục hồi khi cần.</t>
+          <t>10. Toàn bộ file được kiểm tra trước khi ghi. Chỉ cần MỘT dòng sai là không có thay đổi nào được lưu — dữ liệu cũ giữ nguyên.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>12. Bấm nhiều lần cùng một file chỉ ghi một lần (chống double-click bằng request_key + SHA-256).</t>
+          <t>11. Trước mỗi lần nhập, hệ thống tự chụp ảnh (snapshot) toàn bộ đơn giá cũ để phục hồi khi cần.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>12. Bấm nhiều lần cùng một file chỉ ghi một lần (chống double-click bằng request_key + SHA-256).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>13. Chỉ tài khoản ADMIN được nhập file này.</t>
         </is>
